--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11880"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8100"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$108</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -551,9 +551,6 @@
     <t>https://detran.mg.gov.br/atendimento</t>
   </si>
   <si>
-    <t>https://www.transparencia.mg.gov.br/pagina/fale-conosco-portal-da-transparencia</t>
-  </si>
-  <si>
     <t>https://www.mg.gov.br/pagina/ligminas-155</t>
   </si>
   <si>
@@ -756,6 +753,9 @@
   </si>
   <si>
     <t>https://www.transparencia.mg.gov.br/pagina/ata-de-registro-de-precos</t>
+  </si>
+  <si>
+    <t>https://atendimento1.faleconosco.mg.gov.br/ligminas-bpms-frontend/publico/br/gov/prodemge/seplag/ligminasbpms/visao/processos/RegistrarAtendimentoFaleConosco.zul?processo=PROC_00093&amp;atividade=ATIV_00388&amp;site=transparencia</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1118,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>3</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>3</v>
@@ -1174,7 +1174,7 @@
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>3</v>
@@ -1202,21 +1202,21 @@
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>91</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>91</v>
@@ -1239,12 +1239,12 @@
         <v>92</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>91</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>23</v>
@@ -1272,10 +1272,10 @@
     </row>
     <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>52</v>
@@ -1286,21 +1286,21 @@
     </row>
     <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>13</v>
@@ -1328,7 +1328,7 @@
     </row>
     <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>13</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>13</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>13</v>
@@ -1365,12 +1365,12 @@
         <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>13</v>
@@ -1384,13 +1384,13 @@
     </row>
     <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>112</v>
@@ -1398,13 +1398,13 @@
     </row>
     <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>126</v>
@@ -1412,13 +1412,13 @@
     </row>
     <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>113</v>
@@ -1426,27 +1426,27 @@
     </row>
     <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>143</v>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>53</v>
@@ -1468,10 +1468,10 @@
     </row>
     <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>24</v>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>54</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>55</v>
@@ -1510,10 +1510,10 @@
     </row>
     <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>56</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>86</v>
@@ -1538,38 +1538,38 @@
     </row>
     <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>57</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>94</v>
@@ -1594,10 +1594,10 @@
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>35</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>59</v>
@@ -1622,10 +1622,10 @@
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>22</v>
@@ -1636,24 +1636,24 @@
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>60</v>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>46</v>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>58</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>87</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>87</v>
@@ -1720,7 +1720,7 @@
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -1734,10 +1734,10 @@
     </row>
     <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>61</v>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>63</v>
@@ -1762,13 +1762,13 @@
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>124</v>
@@ -1776,13 +1776,13 @@
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>122</v>
@@ -1790,13 +1790,13 @@
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>123</v>
@@ -1804,10 +1804,10 @@
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>62</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>51</v>
@@ -1832,21 +1832,21 @@
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>19</v>
@@ -1855,15 +1855,15 @@
         <v>20</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>65</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>66</v>
@@ -1888,10 +1888,10 @@
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>64</v>
@@ -1902,13 +1902,13 @@
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>159</v>
@@ -1916,7 +1916,7 @@
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>86</v>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>87</v>
@@ -1944,10 +1944,10 @@
     </row>
     <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>25</v>
@@ -1958,7 +1958,7 @@
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>67</v>
@@ -1972,21 +1972,21 @@
     </row>
     <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>46</v>
@@ -2000,21 +2000,21 @@
     </row>
     <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>91</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>73</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>87</v>
@@ -2056,7 +2056,7 @@
     </row>
     <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>87</v>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>70</v>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>74</v>
@@ -2098,10 +2098,10 @@
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>72</v>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>115</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>85</v>
@@ -2140,7 +2140,7 @@
     </row>
     <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>85</v>
@@ -2154,10 +2154,10 @@
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>69</v>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>21</v>
@@ -2182,10 +2182,10 @@
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
@@ -2196,10 +2196,10 @@
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>68</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>50</v>
@@ -2224,13 +2224,13 @@
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>120</v>
@@ -2238,13 +2238,13 @@
     </row>
     <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>119</v>
@@ -2252,13 +2252,13 @@
     </row>
     <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>121</v>
@@ -2266,13 +2266,13 @@
     </row>
     <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>116</v>
@@ -2280,13 +2280,13 @@
     </row>
     <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>116</v>
@@ -2294,13 +2294,13 @@
     </row>
     <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>117</v>
@@ -2308,13 +2308,13 @@
     </row>
     <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>118</v>
@@ -2322,10 +2322,10 @@
     </row>
     <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>28</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="88" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>75</v>
@@ -2350,41 +2350,41 @@
     </row>
     <row r="89" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C89" s="2" t="s">
+      <c r="D89" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>134</v>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="92" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>88</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>88</v>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>71</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>77</v>
@@ -2448,13 +2448,13 @@
     </row>
     <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>170</v>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>37</v>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>78</v>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>78</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>78</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>78</v>
@@ -2527,12 +2527,12 @@
         <v>82</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>174</v>
+        <v>242</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>78</v>
@@ -2541,12 +2541,12 @@
         <v>83</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>78</v>
@@ -2555,12 +2555,12 @@
         <v>84</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>78</v>
@@ -2574,13 +2574,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>115</v>
@@ -2588,13 +2588,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>115</v>
@@ -2602,13 +2602,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>115</v>
@@ -2616,20 +2616,20 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D108" s="3" t="s">
-        <v>242</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D107">
+  <autoFilter ref="A1:D108">
     <sortState ref="A7:D96">
       <sortCondition ref="B1:B107"/>
     </sortState>

--- a/upload/mapadosite.xlsx
+++ b/upload/mapadosite.xlsx
@@ -1,33 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F39A11-DB38-4334-B522-51FC98319C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8100"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$D$109</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="245">
   <si>
     <t>Categoria</t>
   </si>
@@ -756,12 +760,18 @@
   </si>
   <si>
     <t>https://atendimento1.faleconosco.mg.gov.br/ligminas-bpms-frontend/publico/br/gov/prodemge/seplag/ligminasbpms/visao/processos/RegistrarAtendimentoFaleConosco.zul?processo=PROC_00093&amp;atividade=ATIV_00388&amp;site=transparencia</t>
+  </si>
+  <si>
+    <t>Despesas com Eventos Culturais</t>
+  </si>
+  <si>
+    <t>https://www.transparencia.mg.gov.br/pagina/despesas-com-eventos-culturais</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1106,17 +1116,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D108"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D109"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="32.42578125" customWidth="1"/>
+    <col min="1" max="1" width="32.44140625" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="68.5703125" customWidth="1"/>
-    <col min="4" max="4" width="95.28515625" customWidth="1"/>
+    <col min="3" max="3" width="68.5546875" customWidth="1"/>
+    <col min="4" max="4" width="95.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>214</v>
       </c>
@@ -1130,329 +1140,329 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
+        <v>198</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>200</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>198</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>7</v>
+        <v>198</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>199</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
+        <v>78</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>18</v>
+        <v>78</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>216</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>216</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>216</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>215</v>
       </c>
@@ -1466,77 +1476,77 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>24</v>
+        <v>203</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>54</v>
+      <c r="C27" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>215</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>216</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>203</v>
+        <v>86</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>215</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>216</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>212</v>
+        <v>86</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+        <v>182</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>216</v>
       </c>
@@ -1544,27 +1554,27 @@
         <v>86</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>216</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>215</v>
       </c>
@@ -1572,41 +1582,41 @@
         <v>212</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B34" s="2" t="s">
+    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>216</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>215</v>
       </c>
@@ -1620,21 +1630,21 @@
         <v>151</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>216</v>
+    <row r="37" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>215</v>
       </c>
@@ -1642,13 +1652,13 @@
         <v>204</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>215</v>
       </c>
@@ -1656,111 +1666,111 @@
         <v>204</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>216</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>216</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>216</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>87</v>
+        <v>207</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>216</v>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>16</v>
+        <v>207</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>215</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>216</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>63</v>
+        <v>229</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>216</v>
       </c>
@@ -1768,125 +1778,125 @@
         <v>227</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>229</v>
+        <v>87</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>215</v>
+        <v>87</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>216</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>207</v>
+        <v>87</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>216</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>216</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>216</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>65</v>
+        <v>87</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>208</v>
+        <v>87</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>215</v>
       </c>
@@ -1894,363 +1904,363 @@
         <v>208</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="57" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B57" s="2" t="s">
+    <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>216</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>216</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>216</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>216</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>216</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>216</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>216</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>216</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>216</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>216</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>26</v>
+      <c r="C74" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>216</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>220</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>216</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B77" s="2" t="s">
+    <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C79" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>232</v>
+        <v>28</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>216</v>
       </c>
@@ -2258,13 +2268,13 @@
         <v>239</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>216</v>
       </c>
@@ -2272,13 +2282,13 @@
         <v>239</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>216</v>
       </c>
@@ -2286,13 +2296,13 @@
         <v>239</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>216</v>
       </c>
@@ -2300,13 +2310,13 @@
         <v>239</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>216</v>
       </c>
@@ -2314,111 +2324,111 @@
         <v>239</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D88" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="87" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B88" s="2" t="s">
+    <row r="89" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="C89" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>13</v>
+        <v>210</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>197</v>
+        <v>70</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>215</v>
       </c>
@@ -2426,229 +2436,244 @@
         <v>210</v>
       </c>
       <c r="C94" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D97" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="95" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B95" s="2" t="s">
+    <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B96" s="2" t="s">
+    <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C99" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D99" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>83</v>
+        <v>3</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>84</v>
+        <v>3</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>224</v>
+        <v>42</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>190</v>
+        <v>88</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>225</v>
+        <v>43</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
         <v>216</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>226</v>
+        <v>36</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>87</v>
+        <v>192</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>241</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D108">
-    <sortState ref="A7:D96">
-      <sortCondition ref="B1:B107"/>
+  <autoFilter ref="A1:D109" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D109">
+      <sortCondition ref="B1:B109"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1"/>
-    <hyperlink ref="D13" r:id="rId2"/>
-    <hyperlink ref="D31" r:id="rId3"/>
-    <hyperlink ref="D62" r:id="rId4"/>
-    <hyperlink ref="D52" r:id="rId5"/>
-    <hyperlink ref="D90" r:id="rId6"/>
-    <hyperlink ref="D89" r:id="rId7"/>
-    <hyperlink ref="D23" r:id="rId8"/>
-    <hyperlink ref="D7" r:id="rId9"/>
-    <hyperlink ref="D38" r:id="rId10"/>
-    <hyperlink ref="D57" r:id="rId11"/>
-    <hyperlink ref="D108" r:id="rId12"/>
+    <hyperlink ref="D100" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="D79" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="D29" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D31" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="D69" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="D70" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="D108" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="D49" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="D2" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="D37" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="D59" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="D55" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="D32" r:id="rId13" xr:uid="{14300CE4-FAF5-4605-9FA8-B625AC0C5444}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId13"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>